--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-20).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-10-20).xlsx
@@ -938,46 +938,46 @@
     <t>215</t>
   </si>
   <si>
-    <t>61</t>
+    <t>25</t>
   </si>
   <si>
-    <t>R$ 5.131,93</t>
+    <t>R$ 5.027,25</t>
   </si>
   <si>
-    <t>54.5</t>
+    <t>53.4</t>
   </si>
   <si>
-    <t>32.2</t>
+    <t>31.6</t>
   </si>
   <si>
-    <t>5.16</t>
+    <t>5.27</t>
   </si>
   <si>
-    <t>18.4</t>
+    <t>18.6</t>
   </si>
   <si>
-    <t>6.5</t>
+    <t>6.6</t>
   </si>
   <si>
-    <t>5.1</t>
+    <t>6.4</t>
   </si>
   <si>
-    <t>40.6%</t>
+    <t>39.9%</t>
   </si>
   <si>
-    <t>16.2%</t>
+    <t>16.6%</t>
   </si>
   <si>
-    <t>1.5%</t>
+    <t>1.7%</t>
   </si>
   <si>
     <t>0.5%</t>
   </si>
   <si>
-    <t>4.3%</t>
+    <t>4.0%</t>
   </si>
   <si>
-    <t>1.3%</t>
+    <t>1.2%</t>
   </si>
   <si>
     <t>0.3%</t>
@@ -989,43 +989,40 @@
     <t>2.5%</t>
   </si>
   <si>
-    <t>3.2%</t>
+    <t>3.8%</t>
   </si>
   <si>
-    <t>995.0</t>
+    <t>1229.0</t>
   </si>
   <si>
-    <t>798.0</t>
+    <t>999.0</t>
   </si>
   <si>
-    <t>73.0</t>
+    <t>100.0</t>
   </si>
   <si>
-    <t>23.0</t>
+    <t>31.0</t>
   </si>
   <si>
-    <t>214.0</t>
+    <t>240.0</t>
   </si>
   <si>
-    <t>63.0</t>
+    <t>72.0</t>
   </si>
   <si>
     <t>17.0</t>
   </si>
   <si>
-    <t>327.0</t>
+    <t>394.0</t>
   </si>
   <si>
-    <t>122.0</t>
+    <t>148.0</t>
   </si>
   <si>
-    <t>159.0</t>
+    <t>230.0</t>
   </si>
   <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>20.0</t>
+    <t>28.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2212,7 +2209,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>51</v>
@@ -2242,35 +2239,93 @@
         <v>58</v>
       </c>
       <c r="L6" s="4"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="8"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
-      <c r="AB6" s="9"/>
-      <c r="AC6" s="9"/>
-      <c r="AD6" s="6"/>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
-      <c r="AI6" s="6"/>
-      <c r="AJ6" s="6"/>
-      <c r="AK6" s="6"/>
-      <c r="AL6" s="6"/>
-      <c r="AM6" s="6"/>
-      <c r="AN6" s="9"/>
-      <c r="AO6" s="6"/>
+      <c r="M6" s="5">
+        <v>11061.950000000001</v>
+      </c>
+      <c r="N6" s="6">
+        <v>104</v>
+      </c>
+      <c r="O6" s="6">
+        <v>70</v>
+      </c>
+      <c r="P6" s="7">
+        <v>5.1498362745098047</v>
+      </c>
+      <c r="Q6" s="8">
+        <v>13.592028985507246</v>
+      </c>
+      <c r="R6" s="8">
+        <v>1.5151955882352941</v>
+      </c>
+      <c r="S6" s="8">
+        <v>7</v>
+      </c>
+      <c r="T6" s="9">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="U6" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="V6" s="9">
+        <v>0</v>
+      </c>
+      <c r="W6" s="9">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="9">
+        <v>0.014285714285714285</v>
+      </c>
+      <c r="AB6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
       </c>
@@ -2931,7 +2986,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>51</v>
@@ -2961,35 +3016,93 @@
         <v>58</v>
       </c>
       <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="6"/>
+      <c r="M11" s="5">
+        <v>10156.459999999999</v>
+      </c>
+      <c r="N11" s="6">
+        <v>90</v>
+      </c>
+      <c r="O11" s="6">
+        <v>63</v>
+      </c>
+      <c r="P11" s="7">
+        <v>6.1766304347826084</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>19.084392063492064</v>
+      </c>
+      <c r="R11" s="8">
+        <v>6.8420634920634926</v>
+      </c>
+      <c r="S11" s="8">
+        <v>6</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0.015873015873015872</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0.12698412698412698</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="6">
+        <v>8</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP11" s="4">
         <v>58</v>
       </c>
@@ -3497,7 +3610,7 @@
         <v>19519</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C15" s="4">
         <v>51</v>
@@ -3527,35 +3640,93 @@
         <v>58</v>
       </c>
       <c r="L15" s="4"/>
-      <c r="M15" s="5"/>
-      <c r="N15" s="6"/>
-      <c r="O15" s="6"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
-      <c r="S15" s="8"/>
-      <c r="T15" s="9"/>
-      <c r="U15" s="9"/>
-      <c r="V15" s="9"/>
-      <c r="W15" s="9"/>
-      <c r="X15" s="9"/>
-      <c r="Y15" s="9"/>
-      <c r="Z15" s="9"/>
-      <c r="AA15" s="9"/>
-      <c r="AB15" s="9"/>
-      <c r="AC15" s="9"/>
-      <c r="AD15" s="6"/>
-      <c r="AE15" s="6"/>
-      <c r="AF15" s="6"/>
-      <c r="AG15" s="6"/>
-      <c r="AH15" s="6"/>
-      <c r="AI15" s="6"/>
-      <c r="AJ15" s="6"/>
-      <c r="AK15" s="6"/>
-      <c r="AL15" s="6"/>
-      <c r="AM15" s="6"/>
-      <c r="AN15" s="9"/>
-      <c r="AO15" s="6"/>
+      <c r="M15" s="5">
+        <v>16697.150000000001</v>
+      </c>
+      <c r="N15" s="6">
+        <v>214</v>
+      </c>
+      <c r="O15" s="6">
+        <v>91</v>
+      </c>
+      <c r="P15" s="7">
+        <v>6.4535545023696681</v>
+      </c>
+      <c r="Q15" s="8">
+        <v>17.480036263736263</v>
+      </c>
+      <c r="R15" s="8">
+        <v>2.5166670329670326</v>
+      </c>
+      <c r="S15" s="8">
+        <v>7</v>
+      </c>
+      <c r="T15" s="9">
+        <v>0.37362637362637363</v>
+      </c>
+      <c r="U15" s="9">
+        <v>0.17582417582417584</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="9">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9">
+        <v>0.01098901098901099</v>
+      </c>
+      <c r="Y15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="9">
+        <v>0.043956043956043959</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0.02197802197802198</v>
+      </c>
+      <c r="AC15" s="9">
+        <v>0.10989010989010989</v>
+      </c>
+      <c r="AD15" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE15" s="6">
+        <v>16</v>
+      </c>
+      <c r="AF15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL15" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM15" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP15" s="4">
         <v>58</v>
       </c>
@@ -4065,7 +4236,7 @@
         <v>19524</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>51</v>
@@ -4095,35 +4266,93 @@
         <v>58</v>
       </c>
       <c r="L19" s="4"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="8"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="6"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="6"/>
-      <c r="AK19" s="6"/>
-      <c r="AL19" s="6"/>
-      <c r="AM19" s="6"/>
-      <c r="AN19" s="9"/>
-      <c r="AO19" s="6"/>
+      <c r="M19" s="5">
+        <v>6060</v>
+      </c>
+      <c r="N19" s="6">
+        <v>61</v>
+      </c>
+      <c r="O19" s="6">
+        <v>33</v>
+      </c>
+      <c r="P19" s="7">
+        <v>8.1932790322580651</v>
+      </c>
+      <c r="Q19" s="8">
+        <v>24.259090909090908</v>
+      </c>
+      <c r="R19" s="8">
+        <v>8.6072906249999992</v>
+      </c>
+      <c r="S19" s="8">
+        <v>7</v>
+      </c>
+      <c r="T19" s="9">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="U19" s="9">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="V19" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="W19" s="9">
+        <v>0</v>
+      </c>
+      <c r="X19" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="Y19" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="AB19" s="9">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AC19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE19" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP19" s="4">
         <v>58</v>
       </c>
@@ -5360,7 +5589,7 @@
         <v>19546</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>51</v>
@@ -5390,35 +5619,93 @@
         <v>58</v>
       </c>
       <c r="L28" s="4"/>
-      <c r="M28" s="5"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="7"/>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="8"/>
-      <c r="T28" s="9"/>
-      <c r="U28" s="9"/>
-      <c r="V28" s="9"/>
-      <c r="W28" s="9"/>
-      <c r="X28" s="9"/>
-      <c r="Y28" s="9"/>
-      <c r="Z28" s="9"/>
-      <c r="AA28" s="9"/>
-      <c r="AB28" s="9"/>
-      <c r="AC28" s="9"/>
-      <c r="AD28" s="6"/>
-      <c r="AE28" s="6"/>
-      <c r="AF28" s="6"/>
-      <c r="AG28" s="6"/>
-      <c r="AH28" s="6"/>
-      <c r="AI28" s="6"/>
-      <c r="AJ28" s="6"/>
-      <c r="AK28" s="6"/>
-      <c r="AL28" s="6"/>
-      <c r="AM28" s="6"/>
-      <c r="AN28" s="9"/>
-      <c r="AO28" s="6"/>
+      <c r="M28" s="5">
+        <v>6912.1000000000004</v>
+      </c>
+      <c r="N28" s="6">
+        <v>72</v>
+      </c>
+      <c r="O28" s="6">
+        <v>44</v>
+      </c>
+      <c r="P28" s="7">
+        <v>7.0787041666666664</v>
+      </c>
+      <c r="Q28" s="8">
+        <v>26.375</v>
+      </c>
+      <c r="R28" s="8">
+        <v>12.357197727272727</v>
+      </c>
+      <c r="S28" s="8">
+        <v>7</v>
+      </c>
+      <c r="T28" s="9">
+        <v>0.13636363636363635</v>
+      </c>
+      <c r="U28" s="9">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="V28" s="9">
+        <v>0</v>
+      </c>
+      <c r="W28" s="9">
+        <v>0</v>
+      </c>
+      <c r="X28" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Y28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="9">
+        <v>0.15909090909090909</v>
+      </c>
+      <c r="AD28" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE28" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="6">
+        <v>7</v>
+      </c>
+      <c r="AN28" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP28" s="4">
         <v>58</v>
       </c>
@@ -6087,7 +6374,7 @@
         <v>19553</v>
       </c>
       <c r="B33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C33" s="4">
         <v>51</v>
@@ -6115,35 +6402,93 @@
         <v>58</v>
       </c>
       <c r="L33" s="4"/>
-      <c r="M33" s="5"/>
-      <c r="N33" s="6"/>
-      <c r="O33" s="6"/>
-      <c r="P33" s="7"/>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="8"/>
-      <c r="T33" s="9"/>
-      <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
-      <c r="W33" s="9"/>
-      <c r="X33" s="9"/>
-      <c r="Y33" s="9"/>
-      <c r="Z33" s="9"/>
-      <c r="AA33" s="9"/>
-      <c r="AB33" s="9"/>
-      <c r="AC33" s="9"/>
-      <c r="AD33" s="6"/>
-      <c r="AE33" s="6"/>
-      <c r="AF33" s="6"/>
-      <c r="AG33" s="6"/>
-      <c r="AH33" s="6"/>
-      <c r="AI33" s="6"/>
-      <c r="AJ33" s="6"/>
-      <c r="AK33" s="6"/>
-      <c r="AL33" s="6"/>
-      <c r="AM33" s="6"/>
-      <c r="AN33" s="9"/>
-      <c r="AO33" s="6"/>
+      <c r="M33" s="5">
+        <v>5353.25</v>
+      </c>
+      <c r="N33" s="6">
+        <v>42</v>
+      </c>
+      <c r="O33" s="6">
+        <v>29</v>
+      </c>
+      <c r="P33" s="7">
+        <v>3.9150785714285714</v>
+      </c>
+      <c r="Q33" s="8">
+        <v>15.778162068965518</v>
+      </c>
+      <c r="R33" s="8">
+        <v>4.8735620689655175</v>
+      </c>
+      <c r="S33" s="8">
+        <v>7</v>
+      </c>
+      <c r="T33" s="9">
+        <v>0.41379310344827586</v>
+      </c>
+      <c r="U33" s="9">
+        <v>0.13793103448275862</v>
+      </c>
+      <c r="V33" s="9">
+        <v>0</v>
+      </c>
+      <c r="W33" s="9">
+        <v>0.034482758619999998</v>
+      </c>
+      <c r="X33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AB33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE33" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AO33" s="6">
+        <v>2</v>
+      </c>
       <c t="s" r="AP33" s="4">
         <v>58</v>
       </c>
@@ -6967,7 +7312,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -6997,35 +7342,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>5129.0299999999997</v>
+      </c>
+      <c r="N39" s="6">
+        <v>60</v>
+      </c>
+      <c r="O39" s="6">
+        <v>40</v>
+      </c>
+      <c r="P39" s="7">
+        <v>3.192622950819672</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>16.6895825</v>
+      </c>
+      <c r="R39" s="8">
+        <v>6.9185194444444447</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.52500000000000002</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.074999999999999997</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>14</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>7</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -8572,7 +8975,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>51</v>
@@ -8602,35 +9005,93 @@
         <v>58</v>
       </c>
       <c r="L50" s="4"/>
-      <c r="M50" s="5"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="9"/>
-      <c r="U50" s="9"/>
-      <c r="V50" s="9"/>
-      <c r="W50" s="9"/>
-      <c r="X50" s="9"/>
-      <c r="Y50" s="9"/>
-      <c r="Z50" s="9"/>
-      <c r="AA50" s="9"/>
-      <c r="AB50" s="9"/>
-      <c r="AC50" s="9"/>
-      <c r="AD50" s="6"/>
-      <c r="AE50" s="6"/>
-      <c r="AF50" s="6"/>
-      <c r="AG50" s="6"/>
-      <c r="AH50" s="6"/>
-      <c r="AI50" s="6"/>
-      <c r="AJ50" s="6"/>
-      <c r="AK50" s="6"/>
-      <c r="AL50" s="6"/>
-      <c r="AM50" s="6"/>
-      <c r="AN50" s="9"/>
-      <c r="AO50" s="6"/>
+      <c r="M50" s="5">
+        <v>3292.8099999999999</v>
+      </c>
+      <c r="N50" s="6">
+        <v>43</v>
+      </c>
+      <c r="O50" s="6">
+        <v>24</v>
+      </c>
+      <c r="P50" s="7">
+        <v>2.2814386363636365</v>
+      </c>
+      <c r="Q50" s="8">
+        <v>13.770833333333334</v>
+      </c>
+      <c r="R50" s="8">
+        <v>3.8260869565217392</v>
+      </c>
+      <c r="S50" s="8">
+        <v>8</v>
+      </c>
+      <c r="T50" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U50" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V50" s="9">
+        <v>0</v>
+      </c>
+      <c r="W50" s="9">
+        <v>0</v>
+      </c>
+      <c r="X50" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Y50" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="AB50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN50" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP50" s="4">
         <v>58</v>
       </c>
@@ -8671,7 +9132,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -8701,14 +9162,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1419.8599999999999</v>
+      </c>
+      <c r="N51" s="6">
+        <v>15</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.0055533333333333</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>27.443750000000001</v>
+      </c>
+      <c r="R51" s="8">
+        <v>18.002385714285715</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0.125</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -9239,7 +9712,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -9269,35 +9742,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>4202.1000000000004</v>
+      </c>
+      <c r="N55" s="6">
+        <v>50</v>
+      </c>
+      <c r="O55" s="6">
+        <v>36</v>
+      </c>
+      <c r="P55" s="7">
+        <v>3.3196963636363637</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>21.080091666666664</v>
+      </c>
+      <c r="R55" s="8">
+        <v>11.204762857142857</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0.027777777777777776</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9682,33 +10213,79 @@
       <c r="L58" s="4"/>
       <c r="M58" s="5"/>
       <c r="N58" s="6"/>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>47</v>
+      </c>
       <c r="P58" s="7"/>
       <c r="Q58" s="8"/>
       <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9"/>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.14893617021276595</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.085106382978723402</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0.042553191489361701</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0.021276595744680851</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -10216,7 +10793,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>51</v>
@@ -10246,35 +10823,93 @@
         <v>58</v>
       </c>
       <c r="L62" s="4"/>
-      <c r="M62" s="5"/>
-      <c r="N62" s="6"/>
-      <c r="O62" s="6"/>
-      <c r="P62" s="7"/>
-      <c r="Q62" s="8"/>
-      <c r="R62" s="8"/>
-      <c r="S62" s="8"/>
-      <c r="T62" s="9"/>
-      <c r="U62" s="9"/>
-      <c r="V62" s="9"/>
-      <c r="W62" s="9"/>
-      <c r="X62" s="9"/>
-      <c r="Y62" s="9"/>
-      <c r="Z62" s="9"/>
-      <c r="AA62" s="9"/>
-      <c r="AB62" s="9"/>
-      <c r="AC62" s="9"/>
-      <c r="AD62" s="6"/>
-      <c r="AE62" s="6"/>
-      <c r="AF62" s="6"/>
-      <c r="AG62" s="6"/>
-      <c r="AH62" s="6"/>
-      <c r="AI62" s="6"/>
-      <c r="AJ62" s="6"/>
-      <c r="AK62" s="6"/>
-      <c r="AL62" s="6"/>
-      <c r="AM62" s="6"/>
-      <c r="AN62" s="9"/>
-      <c r="AO62" s="6"/>
+      <c r="M62" s="5">
+        <v>3755.21</v>
+      </c>
+      <c r="N62" s="6">
+        <v>31</v>
+      </c>
+      <c r="O62" s="6">
+        <v>18</v>
+      </c>
+      <c r="P62" s="7">
+        <v>2.6387096774193548</v>
+      </c>
+      <c r="Q62" s="8">
+        <v>12.374072222222223</v>
+      </c>
+      <c r="R62" s="8">
+        <v>2.6259277777777776</v>
+      </c>
+      <c r="S62" s="8">
+        <v>7</v>
+      </c>
+      <c r="T62" s="9">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="U62" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="V62" s="9">
+        <v>0</v>
+      </c>
+      <c r="W62" s="9">
+        <v>0</v>
+      </c>
+      <c r="X62" s="9">
+        <v>0.055555555555555552</v>
+      </c>
+      <c r="Y62" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="9">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="AB62" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AC62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD62" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH62" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK62" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL62" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN62" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO62" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP62" s="4">
         <v>58</v>
       </c>
@@ -10472,7 +11107,7 @@
         <v>19633</v>
       </c>
       <c r="B64" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C64" s="4">
         <v>51</v>
@@ -10500,35 +11135,93 @@
         <v>58</v>
       </c>
       <c r="L64" s="4"/>
-      <c r="M64" s="5"/>
-      <c r="N64" s="6"/>
-      <c r="O64" s="6"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="8"/>
-      <c r="R64" s="8"/>
-      <c r="S64" s="8"/>
-      <c r="T64" s="9"/>
-      <c r="U64" s="9"/>
-      <c r="V64" s="9"/>
-      <c r="W64" s="9"/>
-      <c r="X64" s="9"/>
-      <c r="Y64" s="9"/>
-      <c r="Z64" s="9"/>
-      <c r="AA64" s="9"/>
-      <c r="AB64" s="9"/>
-      <c r="AC64" s="9"/>
-      <c r="AD64" s="6"/>
-      <c r="AE64" s="6"/>
-      <c r="AF64" s="6"/>
-      <c r="AG64" s="6"/>
-      <c r="AH64" s="6"/>
-      <c r="AI64" s="6"/>
-      <c r="AJ64" s="6"/>
-      <c r="AK64" s="6"/>
-      <c r="AL64" s="6"/>
-      <c r="AM64" s="6"/>
-      <c r="AN64" s="9"/>
-      <c r="AO64" s="6"/>
+      <c r="M64" s="5">
+        <v>2972.0599999999999</v>
+      </c>
+      <c r="N64" s="6">
+        <v>37</v>
+      </c>
+      <c r="O64" s="6">
+        <v>20</v>
+      </c>
+      <c r="P64" s="7">
+        <v>4.7695228571428574</v>
+      </c>
+      <c r="Q64" s="8">
+        <v>20.390000000000001</v>
+      </c>
+      <c r="R64" s="8">
+        <v>11.341176470588236</v>
+      </c>
+      <c r="S64" s="8">
+        <v>7</v>
+      </c>
+      <c r="T64" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U64" s="9">
+        <v>0.34999999999999998</v>
+      </c>
+      <c r="V64" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="W64" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="X64" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Y64" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Z64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA64" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="AB64" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AC64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD64" s="6">
+        <v>12</v>
+      </c>
+      <c r="AE64" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF64" s="6">
+        <v>4</v>
+      </c>
+      <c r="AG64" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH64" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI64" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL64" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM64" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN64" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO64" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP64" s="4">
         <v>58</v>
       </c>
@@ -11449,7 +12142,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11477,35 +12170,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>4908.8999999999996</v>
+      </c>
+      <c r="N71" s="6">
+        <v>57</v>
+      </c>
+      <c r="O71" s="6">
+        <v>26</v>
+      </c>
+      <c r="P71" s="7">
+        <v>2.747755769230769</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>14.476923076923075</v>
+      </c>
+      <c r="R71" s="8">
+        <v>4.3057956521739129</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.11538461538461539</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0.23076923076923078</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11953,7 +12704,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11983,35 +12734,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>4568.2200000000003</v>
+      </c>
+      <c r="N75" s="6">
+        <v>47</v>
+      </c>
+      <c r="O75" s="6">
+        <v>25</v>
+      </c>
+      <c r="P75" s="7">
+        <v>4.162057446808511</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>16.944000000000003</v>
+      </c>
+      <c r="R75" s="8">
+        <v>5.3286680000000004</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.12</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -13242,7 +14051,7 @@
         <v>19685</v>
       </c>
       <c r="B84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C84" s="4">
         <v>51</v>
@@ -13272,35 +14081,93 @@
         <v>58</v>
       </c>
       <c r="L84" s="4"/>
-      <c r="M84" s="5"/>
-      <c r="N84" s="6"/>
-      <c r="O84" s="6"/>
-      <c r="P84" s="7"/>
-      <c r="Q84" s="8"/>
-      <c r="R84" s="8"/>
-      <c r="S84" s="8"/>
-      <c r="T84" s="9"/>
-      <c r="U84" s="9"/>
-      <c r="V84" s="9"/>
-      <c r="W84" s="9"/>
-      <c r="X84" s="9"/>
-      <c r="Y84" s="9"/>
-      <c r="Z84" s="9"/>
-      <c r="AA84" s="9"/>
-      <c r="AB84" s="9"/>
-      <c r="AC84" s="9"/>
-      <c r="AD84" s="6"/>
-      <c r="AE84" s="6"/>
-      <c r="AF84" s="6"/>
-      <c r="AG84" s="6"/>
-      <c r="AH84" s="6"/>
-      <c r="AI84" s="6"/>
-      <c r="AJ84" s="6"/>
-      <c r="AK84" s="6"/>
-      <c r="AL84" s="6"/>
-      <c r="AM84" s="6"/>
-      <c r="AN84" s="9"/>
-      <c r="AO84" s="6"/>
+      <c r="M84" s="5">
+        <v>3432.6500000000001</v>
+      </c>
+      <c r="N84" s="6">
+        <v>37</v>
+      </c>
+      <c r="O84" s="6">
+        <v>25</v>
+      </c>
+      <c r="P84" s="7">
+        <v>7.1500000000000004</v>
+      </c>
+      <c r="Q84" s="8">
+        <v>20.631332</v>
+      </c>
+      <c r="R84" s="8">
+        <v>7.274240909090909</v>
+      </c>
+      <c r="S84" s="8">
+        <v>7</v>
+      </c>
+      <c r="T84" s="9">
+        <v>0.23999999999999999</v>
+      </c>
+      <c r="U84" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="V84" s="9">
+        <v>0</v>
+      </c>
+      <c r="W84" s="9">
+        <v>0</v>
+      </c>
+      <c r="X84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA84" s="9">
+        <v>0.16</v>
+      </c>
+      <c r="AB84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE84" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="6">
+        <v>4</v>
+      </c>
+      <c r="AL84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM84" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN84" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO84" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP84" s="4">
         <v>58</v>
       </c>
@@ -14378,7 +15245,7 @@
         <v>19700</v>
       </c>
       <c r="B92" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C92" s="4">
         <v>51</v>
@@ -14408,35 +15275,93 @@
         <v>58</v>
       </c>
       <c r="L92" s="4"/>
-      <c r="M92" s="5"/>
-      <c r="N92" s="6"/>
-      <c r="O92" s="6"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="8"/>
-      <c r="R92" s="8"/>
-      <c r="S92" s="8"/>
-      <c r="T92" s="9"/>
-      <c r="U92" s="9"/>
-      <c r="V92" s="9"/>
-      <c r="W92" s="9"/>
-      <c r="X92" s="9"/>
-      <c r="Y92" s="9"/>
-      <c r="Z92" s="9"/>
-      <c r="AA92" s="9"/>
-      <c r="AB92" s="9"/>
-      <c r="AC92" s="9"/>
-      <c r="AD92" s="6"/>
-      <c r="AE92" s="6"/>
-      <c r="AF92" s="6"/>
-      <c r="AG92" s="6"/>
-      <c r="AH92" s="6"/>
-      <c r="AI92" s="6"/>
-      <c r="AJ92" s="6"/>
-      <c r="AK92" s="6"/>
-      <c r="AL92" s="6"/>
-      <c r="AM92" s="6"/>
-      <c r="AN92" s="9"/>
-      <c r="AO92" s="6"/>
+      <c r="M92" s="5">
+        <v>3433.6999999999998</v>
+      </c>
+      <c r="N92" s="6">
+        <v>36</v>
+      </c>
+      <c r="O92" s="6">
+        <v>16</v>
+      </c>
+      <c r="P92" s="7">
+        <v>3.4481472222222225</v>
+      </c>
+      <c r="Q92" s="8">
+        <v>14.195831249999999</v>
+      </c>
+      <c r="R92" s="8">
+        <v>2.4937499999999999</v>
+      </c>
+      <c r="S92" s="8">
+        <v>8</v>
+      </c>
+      <c r="T92" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="U92" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="V92" s="9">
+        <v>0</v>
+      </c>
+      <c r="W92" s="9">
+        <v>0</v>
+      </c>
+      <c r="X92" s="9">
+        <v>0.0625</v>
+      </c>
+      <c r="Y92" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD92" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE92" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM92" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN92" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO92" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP92" s="4">
         <v>58</v>
       </c>
@@ -15234,7 +16159,9 @@
       <c r="N98" s="6">
         <v>26</v>
       </c>
-      <c r="O98" s="6"/>
+      <c r="O98" s="6">
+        <v>22</v>
+      </c>
       <c r="P98" s="7">
         <v>11.798076923076923</v>
       </c>
@@ -15244,31 +16171,75 @@
       <c r="R98" s="8">
         <v>13.735714285714286</v>
       </c>
-      <c r="S98" s="8"/>
+      <c r="S98" s="8">
+        <v>7</v>
+      </c>
       <c r="T98" s="9">
         <v>0</v>
       </c>
-      <c r="U98" s="9"/>
-      <c r="V98" s="9"/>
-      <c r="W98" s="9"/>
-      <c r="X98" s="9"/>
-      <c r="Y98" s="9"/>
-      <c r="Z98" s="9"/>
-      <c r="AA98" s="9"/>
-      <c r="AB98" s="9"/>
-      <c r="AC98" s="9"/>
-      <c r="AD98" s="6"/>
-      <c r="AE98" s="6"/>
-      <c r="AF98" s="6"/>
-      <c r="AG98" s="6"/>
-      <c r="AH98" s="6"/>
-      <c r="AI98" s="6"/>
-      <c r="AJ98" s="6"/>
-      <c r="AK98" s="6"/>
-      <c r="AL98" s="6"/>
-      <c r="AM98" s="6"/>
-      <c r="AN98" s="9"/>
-      <c r="AO98" s="6"/>
+      <c r="U98" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="V98" s="9">
+        <v>0</v>
+      </c>
+      <c r="W98" s="9">
+        <v>0</v>
+      </c>
+      <c r="X98" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z98" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA98" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AB98" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD98" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE98" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF98" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI98" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ98" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL98" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM98" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN98" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO98" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP98" s="4">
         <v>58</v>
       </c>
@@ -15464,7 +16435,7 @@
         <v>19715</v>
       </c>
       <c r="B100" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C100" s="4">
         <v>51</v>
@@ -15494,35 +16465,93 @@
         <v>58</v>
       </c>
       <c r="L100" s="4"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="6"/>
-      <c r="P100" s="7"/>
-      <c r="Q100" s="8"/>
-      <c r="R100" s="8"/>
-      <c r="S100" s="8"/>
-      <c r="T100" s="9"/>
-      <c r="U100" s="9"/>
-      <c r="V100" s="9"/>
-      <c r="W100" s="9"/>
-      <c r="X100" s="9"/>
-      <c r="Y100" s="9"/>
-      <c r="Z100" s="9"/>
-      <c r="AA100" s="9"/>
-      <c r="AB100" s="9"/>
-      <c r="AC100" s="9"/>
-      <c r="AD100" s="6"/>
-      <c r="AE100" s="6"/>
-      <c r="AF100" s="6"/>
-      <c r="AG100" s="6"/>
-      <c r="AH100" s="6"/>
-      <c r="AI100" s="6"/>
-      <c r="AJ100" s="6"/>
-      <c r="AK100" s="6"/>
-      <c r="AL100" s="6"/>
-      <c r="AM100" s="6"/>
-      <c r="AN100" s="9"/>
-      <c r="AO100" s="6"/>
+      <c r="M100" s="5">
+        <v>6959.6000000000004</v>
+      </c>
+      <c r="N100" s="6">
+        <v>74</v>
+      </c>
+      <c r="O100" s="6">
+        <v>33</v>
+      </c>
+      <c r="P100" s="7">
+        <v>14.262612162162162</v>
+      </c>
+      <c r="Q100" s="8">
+        <v>31.071353125000002</v>
+      </c>
+      <c r="R100" s="8">
+        <v>7.8968749999999996</v>
+      </c>
+      <c r="S100" s="8">
+        <v>9</v>
+      </c>
+      <c r="T100" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="U100" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="V100" s="9">
+        <v>0</v>
+      </c>
+      <c r="W100" s="9">
+        <v>0</v>
+      </c>
+      <c r="X100" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="9">
+        <v>0.060606060606060608</v>
+      </c>
+      <c r="AC100" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE100" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL100" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM100" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN100" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO100" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP100" s="4">
         <v>58</v>
       </c>
@@ -15718,7 +16747,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>51</v>
@@ -15748,35 +16777,93 @@
         <v>58</v>
       </c>
       <c r="L102" s="4"/>
-      <c r="M102" s="5"/>
-      <c r="N102" s="6"/>
-      <c r="O102" s="6"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="8"/>
-      <c r="R102" s="8"/>
-      <c r="S102" s="8"/>
-      <c r="T102" s="9"/>
-      <c r="U102" s="9"/>
-      <c r="V102" s="9"/>
-      <c r="W102" s="9"/>
-      <c r="X102" s="9"/>
-      <c r="Y102" s="9"/>
-      <c r="Z102" s="9"/>
-      <c r="AA102" s="9"/>
-      <c r="AB102" s="9"/>
-      <c r="AC102" s="9"/>
-      <c r="AD102" s="6"/>
-      <c r="AE102" s="6"/>
-      <c r="AF102" s="6"/>
-      <c r="AG102" s="6"/>
-      <c r="AH102" s="6"/>
-      <c r="AI102" s="6"/>
-      <c r="AJ102" s="6"/>
-      <c r="AK102" s="6"/>
-      <c r="AL102" s="6"/>
-      <c r="AM102" s="6"/>
-      <c r="AN102" s="9"/>
-      <c r="AO102" s="6"/>
+      <c r="M102" s="5">
+        <v>2432.9200000000001</v>
+      </c>
+      <c r="N102" s="6">
+        <v>30</v>
+      </c>
+      <c r="O102" s="6">
+        <v>20</v>
+      </c>
+      <c r="P102" s="7">
+        <v>5.0202030303030298</v>
+      </c>
+      <c r="Q102" s="8">
+        <v>24.497499999999999</v>
+      </c>
+      <c r="R102" s="8">
+        <v>15.796076470588234</v>
+      </c>
+      <c r="S102" s="8">
+        <v>7</v>
+      </c>
+      <c r="T102" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="U102" s="9">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="V102" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="W102" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="X102" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Y102" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="Z102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="AB102" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AC102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI102" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK102" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL102" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM102" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN102" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO102" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP102" s="4">
         <v>58</v>
       </c>
@@ -16131,7 +17218,7 @@
         <v>19722</v>
       </c>
       <c r="B105" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C105" s="4">
         <v>51</v>
@@ -16159,35 +17246,93 @@
         <v>58</v>
       </c>
       <c r="L105" s="4"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="6"/>
-      <c r="O105" s="6"/>
-      <c r="P105" s="7"/>
-      <c r="Q105" s="8"/>
-      <c r="R105" s="8"/>
-      <c r="S105" s="8"/>
-      <c r="T105" s="9"/>
-      <c r="U105" s="9"/>
-      <c r="V105" s="9"/>
-      <c r="W105" s="9"/>
-      <c r="X105" s="9"/>
-      <c r="Y105" s="9"/>
-      <c r="Z105" s="9"/>
-      <c r="AA105" s="9"/>
-      <c r="AB105" s="9"/>
-      <c r="AC105" s="9"/>
-      <c r="AD105" s="6"/>
-      <c r="AE105" s="6"/>
-      <c r="AF105" s="6"/>
-      <c r="AG105" s="6"/>
-      <c r="AH105" s="6"/>
-      <c r="AI105" s="6"/>
-      <c r="AJ105" s="6"/>
-      <c r="AK105" s="6"/>
-      <c r="AL105" s="6"/>
-      <c r="AM105" s="6"/>
-      <c r="AN105" s="9"/>
-      <c r="AO105" s="6"/>
+      <c r="M105" s="5">
+        <v>4188.6000000000004</v>
+      </c>
+      <c r="N105" s="6">
+        <v>40</v>
+      </c>
+      <c r="O105" s="6">
+        <v>17</v>
+      </c>
+      <c r="P105" s="7">
+        <v>5.5250000000000004</v>
+      </c>
+      <c r="Q105" s="8">
+        <v>23.459805882352942</v>
+      </c>
+      <c r="R105" s="8">
+        <v>10.502941176470589</v>
+      </c>
+      <c r="S105" s="8">
+        <v>6.2999999999999998</v>
+      </c>
+      <c r="T105" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="U105" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="V105" s="9">
+        <v>0</v>
+      </c>
+      <c r="W105" s="9">
+        <v>0</v>
+      </c>
+      <c r="X105" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Y105" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB105" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AC105" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD105" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE105" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH105" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL105" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM105" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN105" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AO105" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP105" s="4">
         <v>58</v>
       </c>
@@ -17648,33 +18793,79 @@
       <c r="L116" s="4"/>
       <c r="M116" s="5"/>
       <c r="N116" s="6"/>
-      <c r="O116" s="6"/>
+      <c r="O116" s="6">
+        <v>14</v>
+      </c>
       <c r="P116" s="7"/>
       <c r="Q116" s="8"/>
       <c r="R116" s="8"/>
-      <c r="S116" s="8"/>
+      <c r="S116" s="8">
+        <v>7</v>
+      </c>
       <c r="T116" s="9"/>
-      <c r="U116" s="9"/>
-      <c r="V116" s="9"/>
-      <c r="W116" s="9"/>
-      <c r="X116" s="9"/>
-      <c r="Y116" s="9"/>
-      <c r="Z116" s="9"/>
-      <c r="AA116" s="9"/>
-      <c r="AB116" s="9"/>
-      <c r="AC116" s="9"/>
-      <c r="AD116" s="6"/>
-      <c r="AE116" s="6"/>
-      <c r="AF116" s="6"/>
-      <c r="AG116" s="6"/>
-      <c r="AH116" s="6"/>
-      <c r="AI116" s="6"/>
-      <c r="AJ116" s="6"/>
-      <c r="AK116" s="6"/>
-      <c r="AL116" s="6"/>
-      <c r="AM116" s="6"/>
-      <c r="AN116" s="9"/>
-      <c r="AO116" s="6"/>
+      <c r="U116" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="V116" s="9">
+        <v>0</v>
+      </c>
+      <c r="W116" s="9">
+        <v>0.071428571428000007</v>
+      </c>
+      <c r="X116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y116" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG116" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM116" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN116" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO116" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP116" s="4">
         <v>58</v>
       </c>
@@ -18965,7 +20156,7 @@
         <v>19756</v>
       </c>
       <c r="B125" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C125" s="4">
         <v>51</v>
@@ -18995,35 +20186,93 @@
         <v>58</v>
       </c>
       <c r="L125" s="4"/>
-      <c r="M125" s="5"/>
-      <c r="N125" s="6"/>
-      <c r="O125" s="6"/>
-      <c r="P125" s="7"/>
-      <c r="Q125" s="8"/>
-      <c r="R125" s="8"/>
-      <c r="S125" s="8"/>
-      <c r="T125" s="9"/>
-      <c r="U125" s="9"/>
-      <c r="V125" s="9"/>
-      <c r="W125" s="9"/>
-      <c r="X125" s="9"/>
-      <c r="Y125" s="9"/>
-      <c r="Z125" s="9"/>
-      <c r="AA125" s="9"/>
-      <c r="AB125" s="9"/>
-      <c r="AC125" s="9"/>
-      <c r="AD125" s="6"/>
-      <c r="AE125" s="6"/>
-      <c r="AF125" s="6"/>
-      <c r="AG125" s="6"/>
-      <c r="AH125" s="6"/>
-      <c r="AI125" s="6"/>
-      <c r="AJ125" s="6"/>
-      <c r="AK125" s="6"/>
-      <c r="AL125" s="6"/>
-      <c r="AM125" s="6"/>
-      <c r="AN125" s="9"/>
-      <c r="AO125" s="6"/>
+      <c r="M125" s="5">
+        <v>12290.440000000001</v>
+      </c>
+      <c r="N125" s="6">
+        <v>69</v>
+      </c>
+      <c r="O125" s="6">
+        <v>51</v>
+      </c>
+      <c r="P125" s="7">
+        <v>4.6235294117647054</v>
+      </c>
+      <c r="Q125" s="8">
+        <v>21.078665999999998</v>
+      </c>
+      <c r="R125" s="8">
+        <v>8.2724489795918377</v>
+      </c>
+      <c r="S125" s="8">
+        <v>8</v>
+      </c>
+      <c r="T125" s="9">
+        <v>0.17999999999999999</v>
+      </c>
+      <c r="U125" s="9">
+        <v>0.27450980392156865</v>
+      </c>
+      <c r="V125" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="W125" s="9">
+        <v>0.019607843137000001</v>
+      </c>
+      <c r="X125" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="Y125" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="Z125" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA125" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="AB125" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AC125" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AD125" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE125" s="6">
+        <v>14</v>
+      </c>
+      <c r="AF125" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG125" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH125" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI125" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ125" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK125" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL125" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM125" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN125" s="9">
+        <v>0.098039215686274508</v>
+      </c>
+      <c r="AO125" s="6">
+        <v>5</v>
+      </c>
       <c t="s" r="AP125" s="4">
         <v>58</v>
       </c>
@@ -19378,7 +20627,7 @@
         <v>19762</v>
       </c>
       <c r="B128" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C128" s="4">
         <v>51</v>
@@ -19408,35 +20657,93 @@
         <v>199</v>
       </c>
       <c r="L128" s="4"/>
-      <c r="M128" s="5"/>
-      <c r="N128" s="6"/>
-      <c r="O128" s="6"/>
-      <c r="P128" s="7"/>
-      <c r="Q128" s="8"/>
-      <c r="R128" s="8"/>
-      <c r="S128" s="8"/>
-      <c r="T128" s="9"/>
-      <c r="U128" s="9"/>
-      <c r="V128" s="9"/>
-      <c r="W128" s="9"/>
-      <c r="X128" s="9"/>
-      <c r="Y128" s="9"/>
-      <c r="Z128" s="9"/>
-      <c r="AA128" s="9"/>
-      <c r="AB128" s="9"/>
-      <c r="AC128" s="9"/>
-      <c r="AD128" s="6"/>
-      <c r="AE128" s="6"/>
-      <c r="AF128" s="6"/>
-      <c r="AG128" s="6"/>
-      <c r="AH128" s="6"/>
-      <c r="AI128" s="6"/>
-      <c r="AJ128" s="6"/>
-      <c r="AK128" s="6"/>
-      <c r="AL128" s="6"/>
-      <c r="AM128" s="6"/>
-      <c r="AN128" s="9"/>
-      <c r="AO128" s="6"/>
+      <c r="M128" s="5">
+        <v>1595.5</v>
+      </c>
+      <c r="N128" s="6">
+        <v>24</v>
+      </c>
+      <c r="O128" s="6">
+        <v>12</v>
+      </c>
+      <c r="P128" s="7">
+        <v>5.747727272727273</v>
+      </c>
+      <c r="Q128" s="8">
+        <v>28.951391666666666</v>
+      </c>
+      <c r="R128" s="8">
+        <v>15.204166666666666</v>
+      </c>
+      <c r="S128" s="8">
+        <v>7</v>
+      </c>
+      <c r="T128" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U128" s="9">
+        <v>0</v>
+      </c>
+      <c r="V128" s="9">
+        <v>0</v>
+      </c>
+      <c r="W128" s="9">
+        <v>0</v>
+      </c>
+      <c r="X128" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y128" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z128" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA128" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB128" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC128" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM128" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN128" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO128" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP128" s="4">
         <v>199</v>
       </c>
@@ -22863,7 +24170,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>51</v>
@@ -22893,35 +24200,93 @@
         <v>58</v>
       </c>
       <c r="L151" s="4"/>
-      <c r="M151" s="5"/>
-      <c r="N151" s="6"/>
-      <c r="O151" s="6"/>
-      <c r="P151" s="7"/>
-      <c r="Q151" s="8"/>
-      <c r="R151" s="8"/>
-      <c r="S151" s="8"/>
-      <c r="T151" s="9"/>
-      <c r="U151" s="9"/>
-      <c r="V151" s="9"/>
-      <c r="W151" s="9"/>
-      <c r="X151" s="9"/>
-      <c r="Y151" s="9"/>
-      <c r="Z151" s="9"/>
-      <c r="AA151" s="9"/>
-      <c r="AB151" s="9"/>
-      <c r="AC151" s="9"/>
-      <c r="AD151" s="6"/>
-      <c r="AE151" s="6"/>
-      <c r="AF151" s="6"/>
-      <c r="AG151" s="6"/>
-      <c r="AH151" s="6"/>
-      <c r="AI151" s="6"/>
-      <c r="AJ151" s="6"/>
-      <c r="AK151" s="6"/>
-      <c r="AL151" s="6"/>
-      <c r="AM151" s="6"/>
-      <c r="AN151" s="9"/>
-      <c r="AO151" s="6"/>
+      <c r="M151" s="5">
+        <v>2151.1700000000001</v>
+      </c>
+      <c r="N151" s="6">
+        <v>29</v>
+      </c>
+      <c r="O151" s="6">
+        <v>22</v>
+      </c>
+      <c r="P151" s="7">
+        <v>3.564941379310345</v>
+      </c>
+      <c r="Q151" s="8">
+        <v>12.352272727272727</v>
+      </c>
+      <c r="R151" s="8">
+        <v>1.6015136363636364</v>
+      </c>
+      <c r="S151" s="8">
+        <v>7</v>
+      </c>
+      <c r="T151" s="9">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="U151" s="9">
+        <v>0</v>
+      </c>
+      <c r="V151" s="9">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9">
+        <v>0</v>
+      </c>
+      <c r="X151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y151" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM151" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN151" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO151" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP151" s="4">
         <v>58</v>
       </c>
@@ -23745,7 +25110,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>51</v>
@@ -23775,35 +25140,93 @@
         <v>58</v>
       </c>
       <c r="L157" s="4"/>
-      <c r="M157" s="5"/>
-      <c r="N157" s="6"/>
-      <c r="O157" s="6"/>
-      <c r="P157" s="7"/>
-      <c r="Q157" s="8"/>
-      <c r="R157" s="8"/>
-      <c r="S157" s="8"/>
-      <c r="T157" s="9"/>
-      <c r="U157" s="9"/>
-      <c r="V157" s="9"/>
-      <c r="W157" s="9"/>
-      <c r="X157" s="9"/>
-      <c r="Y157" s="9"/>
-      <c r="Z157" s="9"/>
-      <c r="AA157" s="9"/>
-      <c r="AB157" s="9"/>
-      <c r="AC157" s="9"/>
-      <c r="AD157" s="6"/>
-      <c r="AE157" s="6"/>
-      <c r="AF157" s="6"/>
-      <c r="AG157" s="6"/>
-      <c r="AH157" s="6"/>
-      <c r="AI157" s="6"/>
-      <c r="AJ157" s="6"/>
-      <c r="AK157" s="6"/>
-      <c r="AL157" s="6"/>
-      <c r="AM157" s="6"/>
-      <c r="AN157" s="9"/>
-      <c r="AO157" s="6"/>
+      <c r="M157" s="5">
+        <v>2278.48</v>
+      </c>
+      <c r="N157" s="6">
+        <v>27</v>
+      </c>
+      <c r="O157" s="6">
+        <v>19</v>
+      </c>
+      <c r="P157" s="7">
+        <v>5.2919740740740737</v>
+      </c>
+      <c r="Q157" s="8">
+        <v>14.79736842105263</v>
+      </c>
+      <c r="R157" s="8">
+        <v>3.0754368421052631</v>
+      </c>
+      <c r="S157" s="8">
+        <v>7</v>
+      </c>
+      <c r="T157" s="9">
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="U157" s="9">
+        <v>0</v>
+      </c>
+      <c r="V157" s="9">
+        <v>0</v>
+      </c>
+      <c r="W157" s="9">
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y157" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM157" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO157" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP157" s="4">
         <v>58</v>
       </c>
@@ -23844,7 +25267,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>51</v>
@@ -23874,35 +25297,93 @@
         <v>58</v>
       </c>
       <c r="L158" s="4"/>
-      <c r="M158" s="5"/>
-      <c r="N158" s="6"/>
-      <c r="O158" s="6"/>
-      <c r="P158" s="7"/>
-      <c r="Q158" s="8"/>
-      <c r="R158" s="8"/>
-      <c r="S158" s="8"/>
-      <c r="T158" s="9"/>
-      <c r="U158" s="9"/>
-      <c r="V158" s="9"/>
-      <c r="W158" s="9"/>
-      <c r="X158" s="9"/>
-      <c r="Y158" s="9"/>
-      <c r="Z158" s="9"/>
-      <c r="AA158" s="9"/>
-      <c r="AB158" s="9"/>
-      <c r="AC158" s="9"/>
-      <c r="AD158" s="6"/>
-      <c r="AE158" s="6"/>
-      <c r="AF158" s="6"/>
-      <c r="AG158" s="6"/>
-      <c r="AH158" s="6"/>
-      <c r="AI158" s="6"/>
-      <c r="AJ158" s="6"/>
-      <c r="AK158" s="6"/>
-      <c r="AL158" s="6"/>
-      <c r="AM158" s="6"/>
-      <c r="AN158" s="9"/>
-      <c r="AO158" s="6"/>
+      <c r="M158" s="5">
+        <v>2384.5799999999999</v>
+      </c>
+      <c r="N158" s="6">
+        <v>25</v>
+      </c>
+      <c r="O158" s="6">
+        <v>20</v>
+      </c>
+      <c r="P158" s="7">
+        <v>7.1256958333333325</v>
+      </c>
+      <c r="Q158" s="8">
+        <v>17.514164999999998</v>
+      </c>
+      <c r="R158" s="8">
+        <v>3.9666684210526313</v>
+      </c>
+      <c r="S158" s="8">
+        <v>7</v>
+      </c>
+      <c r="T158" s="9">
+        <v>0.40000000000000002</v>
+      </c>
+      <c r="U158" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V158" s="9">
+        <v>0</v>
+      </c>
+      <c r="W158" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="X158" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y158" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Z158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA158" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AB158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD158" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AH158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK158" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM158" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN158" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO158" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP158" s="4">
         <v>58</v>
       </c>
@@ -24251,7 +25732,7 @@
         <v>19868</v>
       </c>
       <c r="B161" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C161" s="4">
         <v>51</v>
@@ -24281,10 +25762,16 @@
         <v>58</v>
       </c>
       <c r="L161" s="4"/>
-      <c r="M161" s="5"/>
-      <c r="N161" s="6"/>
+      <c r="M161" s="5">
+        <v>3709.6500000000001</v>
+      </c>
+      <c r="N161" s="6">
+        <v>47</v>
+      </c>
       <c r="O161" s="6"/>
-      <c r="P161" s="7"/>
+      <c r="P161" s="7">
+        <v>9.2595825000000005</v>
+      </c>
       <c r="Q161" s="8"/>
       <c r="R161" s="8"/>
       <c r="S161" s="8"/>
@@ -24350,7 +25837,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24380,35 +25867,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>3518.5</v>
+      </c>
+      <c r="N162" s="6">
+        <v>38</v>
+      </c>
+      <c r="O162" s="6">
+        <v>24</v>
+      </c>
+      <c r="P162" s="7">
+        <v>7.0040540540540537</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>18.771529166666667</v>
+      </c>
+      <c r="R162" s="8">
+        <v>4.8050739130434783</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0.083333333332999998</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>6</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -24763,7 +26308,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>51</v>
@@ -24793,35 +26338,93 @@
         <v>58</v>
       </c>
       <c r="L165" s="4"/>
-      <c r="M165" s="5"/>
-      <c r="N165" s="6"/>
-      <c r="O165" s="6"/>
-      <c r="P165" s="7"/>
-      <c r="Q165" s="8"/>
-      <c r="R165" s="8"/>
-      <c r="S165" s="8"/>
-      <c r="T165" s="9"/>
-      <c r="U165" s="9"/>
-      <c r="V165" s="9"/>
-      <c r="W165" s="9"/>
-      <c r="X165" s="9"/>
-      <c r="Y165" s="9"/>
-      <c r="Z165" s="9"/>
-      <c r="AA165" s="9"/>
-      <c r="AB165" s="9"/>
-      <c r="AC165" s="9"/>
-      <c r="AD165" s="6"/>
-      <c r="AE165" s="6"/>
-      <c r="AF165" s="6"/>
-      <c r="AG165" s="6"/>
-      <c r="AH165" s="6"/>
-      <c r="AI165" s="6"/>
-      <c r="AJ165" s="6"/>
-      <c r="AK165" s="6"/>
-      <c r="AL165" s="6"/>
-      <c r="AM165" s="6"/>
-      <c r="AN165" s="9"/>
-      <c r="AO165" s="6"/>
+      <c r="M165" s="5">
+        <v>3005.98</v>
+      </c>
+      <c r="N165" s="6">
+        <v>35</v>
+      </c>
+      <c r="O165" s="6">
+        <v>19</v>
+      </c>
+      <c r="P165" s="7">
+        <v>9.0725499999999997</v>
+      </c>
+      <c r="Q165" s="8">
+        <v>17.328947368421051</v>
+      </c>
+      <c r="R165" s="8">
+        <v>1.0157894736842106</v>
+      </c>
+      <c r="S165" s="8">
+        <v>7</v>
+      </c>
+      <c r="T165" s="9">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="U165" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="V165" s="9">
+        <v>0</v>
+      </c>
+      <c r="W165" s="9">
+        <v>0</v>
+      </c>
+      <c r="X165" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="Y165" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH165" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM165" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN165" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO165" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP165" s="4">
         <v>58</v>
       </c>
@@ -27209,7 +28812,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -27239,35 +28842,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>4085.3000000000002</v>
+      </c>
+      <c r="N181" s="6">
+        <v>41</v>
+      </c>
+      <c r="O181" s="6">
+        <v>26</v>
+      </c>
+      <c r="P181" s="7">
+        <v>3.5654175000000001</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>12.342307692307692</v>
+      </c>
+      <c r="R181" s="8">
+        <v>2.3944444444444444</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0.19230769230769232</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>19</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>12</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27465,7 +29126,7 @@
         <v>19912</v>
       </c>
       <c r="B183" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C183" s="4">
         <v>51</v>
@@ -27495,35 +29156,93 @@
         <v>58</v>
       </c>
       <c r="L183" s="4"/>
-      <c r="M183" s="5"/>
-      <c r="N183" s="6"/>
-      <c r="O183" s="6"/>
-      <c r="P183" s="7"/>
-      <c r="Q183" s="8"/>
-      <c r="R183" s="8"/>
-      <c r="S183" s="8"/>
-      <c r="T183" s="9"/>
-      <c r="U183" s="9"/>
-      <c r="V183" s="9"/>
-      <c r="W183" s="9"/>
-      <c r="X183" s="9"/>
-      <c r="Y183" s="9"/>
-      <c r="Z183" s="9"/>
-      <c r="AA183" s="9"/>
-      <c r="AB183" s="9"/>
-      <c r="AC183" s="9"/>
-      <c r="AD183" s="6"/>
-      <c r="AE183" s="6"/>
-      <c r="AF183" s="6"/>
-      <c r="AG183" s="6"/>
-      <c r="AH183" s="6"/>
-      <c r="AI183" s="6"/>
-      <c r="AJ183" s="6"/>
-      <c r="AK183" s="6"/>
-      <c r="AL183" s="6"/>
-      <c r="AM183" s="6"/>
-      <c r="AN183" s="9"/>
-      <c r="AO183" s="6"/>
+      <c r="M183" s="5">
+        <v>2899.6399999999999</v>
+      </c>
+      <c r="N183" s="6">
+        <v>39</v>
+      </c>
+      <c r="O183" s="6">
+        <v>18</v>
+      </c>
+      <c r="P183" s="7">
+        <v>5.234342424242425</v>
+      </c>
+      <c r="Q183" s="8">
+        <v>15.053705555555556</v>
+      </c>
+      <c r="R183" s="8">
+        <v>2.0127470588235297</v>
+      </c>
+      <c r="S183" s="8">
+        <v>8</v>
+      </c>
+      <c r="T183" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U183" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="V183" s="9">
+        <v>0</v>
+      </c>
+      <c r="W183" s="9">
+        <v>0</v>
+      </c>
+      <c r="X183" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y183" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA183" s="9">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="AB183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD183" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE183" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK183" s="6">
+        <v>5</v>
+      </c>
+      <c r="AL183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM183" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN183" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO183" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP183" s="4">
         <v>58</v>
       </c>
@@ -27919,7 +29638,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27949,35 +29668,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>1504.05</v>
+      </c>
+      <c r="N187" s="6">
+        <v>18</v>
+      </c>
+      <c r="O187" s="6">
+        <v>14</v>
+      </c>
+      <c r="P187" s="7">
+        <v>8.9240722222222217</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>31.148807142857144</v>
+      </c>
+      <c r="R187" s="8">
+        <v>16.323807142857142</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -28175,7 +29952,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -28205,35 +29982,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>5077.6899999999996</v>
+      </c>
+      <c r="N189" s="6">
+        <v>75</v>
+      </c>
+      <c r="O189" s="6">
+        <v>65</v>
+      </c>
+      <c r="P189" s="7">
+        <v>5.1133333333333333</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>23.562819999999999</v>
+      </c>
+      <c r="R189" s="8">
+        <v>11.769010937499999</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.1076923076923077</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.47692307692307695</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.46153846153846156</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>34</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>31</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>30</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -28274,7 +30109,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -28304,35 +30139,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>3315.5500000000002</v>
+      </c>
+      <c r="N190" s="6">
+        <v>42</v>
+      </c>
+      <c r="O190" s="6">
+        <v>15</v>
+      </c>
+      <c r="P190" s="7">
+        <v>9.1504174999999996</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>15.941113333333334</v>
+      </c>
+      <c r="R190" s="8">
+        <v>6.0583357142857137</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0.066666666666666666</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -29627,7 +31520,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -29657,35 +31550,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>3158.3600000000001</v>
+      </c>
+      <c r="N199" s="6">
+        <v>32</v>
+      </c>
+      <c r="O199" s="6">
+        <v>21</v>
+      </c>
+      <c r="P199" s="7">
+        <v>4.4849451612903222</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>16.701585714285713</v>
+      </c>
+      <c r="R199" s="8">
+        <v>4.9611095238095242</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -30395,7 +32346,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>51</v>
@@ -30425,35 +32376,93 @@
         <v>58</v>
       </c>
       <c r="L205" s="4"/>
-      <c r="M205" s="5"/>
-      <c r="N205" s="6"/>
-      <c r="O205" s="6"/>
-      <c r="P205" s="7"/>
-      <c r="Q205" s="8"/>
-      <c r="R205" s="8"/>
-      <c r="S205" s="8"/>
-      <c r="T205" s="9"/>
-      <c r="U205" s="9"/>
-      <c r="V205" s="9"/>
-      <c r="W205" s="9"/>
-      <c r="X205" s="9"/>
-      <c r="Y205" s="9"/>
-      <c r="Z205" s="9"/>
-      <c r="AA205" s="9"/>
-      <c r="AB205" s="9"/>
-      <c r="AC205" s="9"/>
-      <c r="AD205" s="6"/>
-      <c r="AE205" s="6"/>
-      <c r="AF205" s="6"/>
-      <c r="AG205" s="6"/>
-      <c r="AH205" s="6"/>
-      <c r="AI205" s="6"/>
-      <c r="AJ205" s="6"/>
-      <c r="AK205" s="6"/>
-      <c r="AL205" s="6"/>
-      <c r="AM205" s="6"/>
-      <c r="AN205" s="9"/>
-      <c r="AO205" s="6"/>
+      <c r="M205" s="5">
+        <v>2515.3000000000002</v>
+      </c>
+      <c r="N205" s="6">
+        <v>30</v>
+      </c>
+      <c r="O205" s="6">
+        <v>12</v>
+      </c>
+      <c r="P205" s="7">
+        <v>4.9249999999999998</v>
+      </c>
+      <c r="Q205" s="8">
+        <v>15.011111111111111</v>
+      </c>
+      <c r="R205" s="8">
+        <v>3.5111111111111111</v>
+      </c>
+      <c r="S205" s="8">
+        <v>7</v>
+      </c>
+      <c r="T205" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U205" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="V205" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="W205" s="9">
+        <v>0</v>
+      </c>
+      <c r="X205" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y205" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="Z205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="AB205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD205" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF205" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI205" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK205" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN205" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO205" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP205" s="4">
         <v>58</v>
       </c>
@@ -30494,7 +32503,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>51</v>
@@ -30524,35 +32533,93 @@
         <v>58</v>
       </c>
       <c r="L206" s="4"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="6"/>
-      <c r="O206" s="6"/>
-      <c r="P206" s="7"/>
-      <c r="Q206" s="8"/>
-      <c r="R206" s="8"/>
-      <c r="S206" s="8"/>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
-      <c r="V206" s="9"/>
-      <c r="W206" s="9"/>
-      <c r="X206" s="9"/>
-      <c r="Y206" s="9"/>
-      <c r="Z206" s="9"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-      <c r="AC206" s="9"/>
-      <c r="AD206" s="6"/>
-      <c r="AE206" s="6"/>
-      <c r="AF206" s="6"/>
-      <c r="AG206" s="6"/>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="9"/>
-      <c r="AO206" s="6"/>
+      <c r="M206" s="5">
+        <v>1950.6300000000001</v>
+      </c>
+      <c r="N206" s="6">
+        <v>20</v>
+      </c>
+      <c r="O206" s="6">
+        <v>8</v>
+      </c>
+      <c r="P206" s="7">
+        <v>7.3398166666666675</v>
+      </c>
+      <c r="Q206" s="8">
+        <v>21.118749999999999</v>
+      </c>
+      <c r="R206" s="8">
+        <v>6.75</v>
+      </c>
+      <c r="S206" s="8">
+        <v>7</v>
+      </c>
+      <c r="T206" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="U206" s="9">
+        <v>0</v>
+      </c>
+      <c r="V206" s="9">
+        <v>0</v>
+      </c>
+      <c r="W206" s="9">
+        <v>0</v>
+      </c>
+      <c r="X206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP206" s="4">
         <v>58</v>
       </c>
@@ -31047,7 +33114,7 @@
         <v>19966</v>
       </c>
       <c r="B211" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C211" s="4">
         <v>51</v>
@@ -31077,35 +33144,93 @@
         <v>58</v>
       </c>
       <c r="L211" s="4"/>
-      <c r="M211" s="5"/>
-      <c r="N211" s="6"/>
-      <c r="O211" s="6"/>
-      <c r="P211" s="7"/>
-      <c r="Q211" s="8"/>
-      <c r="R211" s="8"/>
-      <c r="S211" s="8"/>
-      <c r="T211" s="9"/>
-      <c r="U211" s="9"/>
-      <c r="V211" s="9"/>
-      <c r="W211" s="9"/>
-      <c r="X211" s="9"/>
-      <c r="Y211" s="9"/>
-      <c r="Z211" s="9"/>
-      <c r="AA211" s="9"/>
-      <c r="AB211" s="9"/>
-      <c r="AC211" s="9"/>
-      <c r="AD211" s="6"/>
-      <c r="AE211" s="6"/>
-      <c r="AF211" s="6"/>
-      <c r="AG211" s="6"/>
-      <c r="AH211" s="6"/>
-      <c r="AI211" s="6"/>
-      <c r="AJ211" s="6"/>
-      <c r="AK211" s="6"/>
-      <c r="AL211" s="6"/>
-      <c r="AM211" s="6"/>
-      <c r="AN211" s="9"/>
-      <c r="AO211" s="6"/>
+      <c r="M211" s="5">
+        <v>2483.21</v>
+      </c>
+      <c r="N211" s="6">
+        <v>30</v>
+      </c>
+      <c r="O211" s="6">
+        <v>17</v>
+      </c>
+      <c r="P211" s="7">
+        <v>5.7862068965517244</v>
+      </c>
+      <c r="Q211" s="8">
+        <v>24.99791875</v>
+      </c>
+      <c r="R211" s="8">
+        <v>12.422918749999999</v>
+      </c>
+      <c r="S211" s="8">
+        <v>7</v>
+      </c>
+      <c r="T211" s="9">
+        <v>0.1875</v>
+      </c>
+      <c r="U211" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V211" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="W211" s="9">
+        <v>0</v>
+      </c>
+      <c r="X211" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y211" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA211" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="AB211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD211" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE211" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF211" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG211" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH211" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI211" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ211" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK211" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL211" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM211" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN211" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO211" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP211" s="4">
         <v>58</v>
       </c>
@@ -31791,10 +33916,10 @@
         <v>336</v>
       </c>
       <c t="s" r="AN217" s="11">
+        <v>320</v>
+      </c>
+      <c t="s" r="AO217" s="11">
         <v>337</v>
-      </c>
-      <c t="s" r="AO217" s="11">
-        <v>338</v>
       </c>
       <c r="AP217" s="12"/>
       <c t="s" r="AQ217" s="12">
@@ -31811,10 +33936,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX217" s="11">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c t="s" r="AY217" s="11">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AZ217" s="12"/>
       <c r="BA217" s="12"/>
